--- a/Lower_mantle_rate.xlsx
+++ b/Lower_mantle_rate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,11 @@
           <t>Error_old</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Lower mantle rate (mm/yr)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -513,6 +518,9 @@
       <c r="J2" t="n">
         <v>120</v>
       </c>
+      <c r="K2" t="n">
+        <v>9.463442868979588</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -547,6 +555,9 @@
       <c r="J3" t="n">
         <v>120</v>
       </c>
+      <c r="K3" t="n">
+        <v>9.463442868979588</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -581,6 +592,9 @@
       <c r="J4" t="n">
         <v>90</v>
       </c>
+      <c r="K4" t="n">
+        <v>12.20028150573651</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -615,6 +629,9 @@
       <c r="J5" t="n">
         <v>50</v>
       </c>
+      <c r="K5" t="n">
+        <v>8.434480662127971</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -649,6 +666,9 @@
       <c r="J6" t="n">
         <v>160</v>
       </c>
+      <c r="K6" t="n">
+        <v>10.18329028177691</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -683,6 +703,9 @@
       <c r="J7" t="n">
         <v>225</v>
       </c>
+      <c r="K7" t="n">
+        <v>10.79040543998855</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -717,6 +740,9 @@
       <c r="J8" t="n">
         <v>95</v>
       </c>
+      <c r="K8" t="n">
+        <v>5.572011246936405</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -751,6 +777,9 @@
       <c r="J9" t="n">
         <v>108</v>
       </c>
+      <c r="K9" t="n">
+        <v>6.793074293125489</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -785,6 +814,9 @@
       <c r="J10" t="n">
         <v>100</v>
       </c>
+      <c r="K10" t="n">
+        <v>6.487468207264103</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +851,9 @@
       <c r="J11" t="n">
         <v>90</v>
       </c>
+      <c r="K11" t="n">
+        <v>16.12514240873575</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -853,6 +888,9 @@
       <c r="J12" t="n">
         <v>50</v>
       </c>
+      <c r="K12" t="n">
+        <v>8.538798444675361</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -887,6 +925,9 @@
       <c r="J13" t="n">
         <v>260</v>
       </c>
+      <c r="K13" t="n">
+        <v>9.36643434099677</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -921,6 +962,9 @@
       <c r="J14" t="n">
         <v>250</v>
       </c>
+      <c r="K14" t="n">
+        <v>9.797613617156177</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,6 +999,9 @@
       <c r="J15" t="n">
         <v>225</v>
       </c>
+      <c r="K15" t="n">
+        <v>9.821081620308954</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -989,6 +1036,9 @@
       <c r="J16" t="n">
         <v>34</v>
       </c>
+      <c r="K16" t="n">
+        <v>13.7744323280313</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1023,6 +1073,9 @@
       <c r="J17" t="n">
         <v>70</v>
       </c>
+      <c r="K17" t="n">
+        <v>7.124862941423252</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1057,6 +1110,9 @@
       <c r="J18" t="n">
         <v>200</v>
       </c>
+      <c r="K18" t="n">
+        <v>11.16950208297851</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1091,6 +1147,9 @@
       <c r="J19" t="n">
         <v>55</v>
       </c>
+      <c r="K19" t="n">
+        <v>8.044221962126416</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1125,6 +1184,9 @@
       <c r="J20" t="n">
         <v>68</v>
       </c>
+      <c r="K20" t="n">
+        <v>11.62885015087499</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1159,6 +1221,9 @@
       <c r="J21" t="n">
         <v>26</v>
       </c>
+      <c r="K21" t="n">
+        <v>19.69230056502149</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1193,6 +1258,9 @@
       <c r="J22" t="n">
         <v>40</v>
       </c>
+      <c r="K22" t="n">
+        <v>12.36528006110572</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1227,6 +1295,9 @@
       <c r="J23" t="n">
         <v>40</v>
       </c>
+      <c r="K23" t="n">
+        <v>12.36528006110572</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1261,6 +1332,9 @@
       <c r="J24" t="n">
         <v>64</v>
       </c>
+      <c r="K24" t="n">
+        <v>12.32941769876088</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1295,6 +1369,9 @@
       <c r="J25" t="n">
         <v>202.5</v>
       </c>
+      <c r="K25" t="n">
+        <v>9.24099345915427</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1329,6 +1406,9 @@
       <c r="J26" t="n">
         <v>151.5</v>
       </c>
+      <c r="K26" t="n">
+        <v>7.620160289304716</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1363,6 +1443,9 @@
       <c r="J27" t="n">
         <v>170</v>
       </c>
+      <c r="K27" t="n">
+        <v>13.61156307812197</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1397,6 +1480,9 @@
       <c r="J28" t="n">
         <v>66</v>
       </c>
+      <c r="K28" t="n">
+        <v>9.960985948392659</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1431,6 +1517,9 @@
       <c r="J29" t="n">
         <v>204</v>
       </c>
+      <c r="K29" t="n">
+        <v>9.656832703750755</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1465,6 +1554,9 @@
       <c r="J30" t="n">
         <v>150</v>
       </c>
+      <c r="K30" t="n">
+        <v>9.282346127886584</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1499,6 +1591,9 @@
       <c r="J31" t="n">
         <v>240</v>
       </c>
+      <c r="K31" t="n">
+        <v>7.496033918488747</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1533,6 +1628,9 @@
       <c r="J32" t="n">
         <v>129.5</v>
       </c>
+      <c r="K32" t="n">
+        <v>11.65461236003016</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1567,6 +1665,9 @@
       <c r="J33" t="n">
         <v>50</v>
       </c>
+      <c r="K33" t="n">
+        <v>19.48505028377214</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1601,6 +1702,9 @@
       <c r="J34" t="n">
         <v>90</v>
       </c>
+      <c r="K34" t="n">
+        <v>8.331835149609207</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1635,6 +1739,9 @@
       <c r="J35" t="n">
         <v>116</v>
       </c>
+      <c r="K35" t="n">
+        <v>11.9068675000933</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1669,6 +1776,9 @@
       <c r="J36" t="n">
         <v>144.5</v>
       </c>
+      <c r="K36" t="n">
+        <v>8.50488695779767</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1703,6 +1813,9 @@
       <c r="J37" t="n">
         <v>95</v>
       </c>
+      <c r="K37" t="n">
+        <v>14.86304468946089</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1737,6 +1850,9 @@
       <c r="J38" t="n">
         <v>52</v>
       </c>
+      <c r="K38" t="n">
+        <v>10.04727155528581</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1771,6 +1887,9 @@
       <c r="J39" t="n">
         <v>85</v>
       </c>
+      <c r="K39" t="n">
+        <v>5.789097939095087</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1805,6 +1924,9 @@
       <c r="J40" t="n">
         <v>45</v>
       </c>
+      <c r="K40" t="n">
+        <v>21.05244723241917</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1839,6 +1961,9 @@
       <c r="J41" t="n">
         <v>52</v>
       </c>
+      <c r="K41" t="n">
+        <v>15.15469879657149</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1873,6 +1998,9 @@
       <c r="J42" t="n">
         <v>150</v>
       </c>
+      <c r="K42" t="n">
+        <v>11.7933857040472</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1907,6 +2035,9 @@
       <c r="J43" t="n">
         <v>63.5</v>
       </c>
+      <c r="K43" t="n">
+        <v>11.25591569128764</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1941,6 +2072,9 @@
       <c r="J44" t="n">
         <v>150</v>
       </c>
+      <c r="K44" t="n">
+        <v>7.713912661766724</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1975,6 +2109,9 @@
       <c r="J45" t="n">
         <v>136.5</v>
       </c>
+      <c r="K45" t="n">
+        <v>6.3149856512745</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2009,6 +2146,9 @@
       <c r="J46" t="n">
         <v>77</v>
       </c>
+      <c r="K46" t="n">
+        <v>12.20493437048467</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2043,6 +2183,9 @@
       <c r="J47" t="n">
         <v>60</v>
       </c>
+      <c r="K47" t="n">
+        <v>5.297956494373893</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2077,6 +2220,9 @@
       <c r="J48" t="n">
         <v>52</v>
       </c>
+      <c r="K48" t="n">
+        <v>19.18115478736383</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2111,6 +2257,9 @@
       <c r="J49" t="n">
         <v>35</v>
       </c>
+      <c r="K49" t="n">
+        <v>14.98742368674479</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2145,6 +2294,9 @@
       <c r="J50" t="n">
         <v>180</v>
       </c>
+      <c r="K50" t="n">
+        <v>8.395563964176922</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2179,6 +2331,9 @@
       <c r="J51" t="n">
         <v>112.5</v>
       </c>
+      <c r="K51" t="n">
+        <v>12.88280546110065</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2213,6 +2368,9 @@
       <c r="J52" t="n">
         <v>62.5</v>
       </c>
+      <c r="K52" t="n">
+        <v>11.05573562788212</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2247,6 +2405,9 @@
       <c r="J53" t="n">
         <v>124.5</v>
       </c>
+      <c r="K53" t="n">
+        <v>11.89037147845542</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2281,6 +2442,9 @@
       <c r="J54" t="n">
         <v>195</v>
       </c>
+      <c r="K54" t="n">
+        <v>10.70598915563385</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2315,6 +2479,9 @@
       <c r="J55" t="n">
         <v>160</v>
       </c>
+      <c r="K55" t="n">
+        <v>9.808751350485537</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2349,6 +2516,9 @@
       <c r="J56" t="n">
         <v>61</v>
       </c>
+      <c r="K56" t="n">
+        <v>14.05381152889121</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2383,6 +2553,9 @@
       <c r="J57" t="n">
         <v>90</v>
       </c>
+      <c r="K57" t="n">
+        <v>5.505575909281604</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2417,6 +2590,9 @@
       <c r="J58" t="n">
         <v>117.5</v>
       </c>
+      <c r="K58" t="n">
+        <v>11.87773919503311</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2451,6 +2627,9 @@
       <c r="J59" t="n">
         <v>203.5</v>
       </c>
+      <c r="K59" t="n">
+        <v>12.69070991700661</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2485,6 +2664,9 @@
       <c r="J60" t="n">
         <v>83.5</v>
       </c>
+      <c r="K60" t="n">
+        <v>5.555636491076954</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2519,6 +2701,9 @@
       <c r="J61" t="n">
         <v>30</v>
       </c>
+      <c r="K61" t="n">
+        <v>13.40386922193979</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2553,6 +2738,9 @@
       <c r="J62" t="n">
         <v>73</v>
       </c>
+      <c r="K62" t="n">
+        <v>5.612939292284702</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2587,6 +2775,9 @@
       <c r="J63" t="n">
         <v>235</v>
       </c>
+      <c r="K63" t="n">
+        <v>9.509656880454299</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2621,6 +2812,9 @@
       <c r="J64" t="n">
         <v>80</v>
       </c>
+      <c r="K64" t="n">
+        <v>7.124862941423252</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2655,6 +2849,9 @@
       <c r="J65" t="n">
         <v>150</v>
       </c>
+      <c r="K65" t="n">
+        <v>8.270204440259517</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2689,6 +2886,9 @@
       <c r="J66" t="n">
         <v>79.5</v>
       </c>
+      <c r="K66" t="n">
+        <v>12.98232753394446</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2723,6 +2923,9 @@
       <c r="J67" t="n">
         <v>131.5</v>
       </c>
+      <c r="K67" t="n">
+        <v>10.45404931667708</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2757,6 +2960,9 @@
       <c r="J68" t="n">
         <v>52.5</v>
       </c>
+      <c r="K68" t="n">
+        <v>17.73721668653382</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2791,6 +2997,9 @@
       <c r="J69" t="n">
         <v>146.5</v>
       </c>
+      <c r="K69" t="n">
+        <v>8.978628563237443</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2825,6 +3034,9 @@
       <c r="J70" t="n">
         <v>50</v>
       </c>
+      <c r="K70" t="n">
+        <v>17.32873802007647</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2859,6 +3071,9 @@
       <c r="J71" t="n">
         <v>85</v>
       </c>
+      <c r="K71" t="n">
+        <v>23.79082350303748</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2893,6 +3108,9 @@
       <c r="J72" t="n">
         <v>205.5</v>
       </c>
+      <c r="K72" t="n">
+        <v>11.61715229366708</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2927,6 +3145,9 @@
       <c r="J73" t="n">
         <v>88.5</v>
       </c>
+      <c r="K73" t="n">
+        <v>10.00284911691323</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2961,6 +3182,9 @@
       <c r="J74" t="n">
         <v>102.5</v>
       </c>
+      <c r="K74" t="n">
+        <v>7.213577651351256</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2995,6 +3219,9 @@
       <c r="J75" t="n">
         <v>205.5</v>
       </c>
+      <c r="K75" t="n">
+        <v>10.30596128986719</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3029,6 +3256,9 @@
       <c r="J76" t="n">
         <v>76</v>
       </c>
+      <c r="K76" t="n">
+        <v>8.626472637381365</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3062,6 +3292,9 @@
       </c>
       <c r="J77" t="n">
         <v>70</v>
+      </c>
+      <c r="K77" t="n">
+        <v>10.04578760019442</v>
       </c>
     </row>
   </sheetData>
